--- a/data/google/Keyword/Keyword-July-week5.xlsx
+++ b/data/google/Keyword/Keyword-July-week5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hafiz.yap\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931AD8BB-6B24-47C9-9A10-5201536C5F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366A552B-13AE-48A4-9062-DAF8EE4029E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="96">
   <si>
     <t>Search keyword report</t>
   </si>
@@ -73,244 +73,241 @@
     <t>Enabled</t>
   </si>
   <si>
+    <t>[ห้าง ทอง เยาวราช กรุงเทพ]</t>
+  </si>
+  <si>
+    <t>Exact match</t>
+  </si>
+  <si>
+    <t>4040 | ONN | Search Brand Traffic | Always On</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Not eligible</t>
+  </si>
+  <si>
+    <t>campaign paused</t>
+  </si>
+  <si>
+    <t>THB</t>
+  </si>
+  <si>
+    <t>"ทองกรุงเทพเยาวราช"</t>
+  </si>
+  <si>
+    <t>Phrase match</t>
+  </si>
+  <si>
+    <t>"ร้านทอง โรบินสัน"</t>
+  </si>
+  <si>
+    <t>Paused</t>
+  </si>
+  <si>
+    <t>"ร้านทอ"</t>
+  </si>
+  <si>
+    <t>paused; campaign paused</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>[ห้าง ทอง ออ โร ร่า ใกล้ ฉัน]</t>
+  </si>
+  <si>
+    <t>"ร้านทองออนไลน์"</t>
+  </si>
+  <si>
+    <t>"ร้านทองกรุงเทพเยาวราช"</t>
+  </si>
+  <si>
+    <t>ห้างทองใกล้ฉัน</t>
+  </si>
+  <si>
+    <t>Broad match</t>
+  </si>
+  <si>
+    <t>"ร้านทองใกล้ฉัน"</t>
+  </si>
+  <si>
+    <t>[Bangkok Golds]</t>
+  </si>
+  <si>
+    <t>"ร้านเพชรทองออโรร่า"</t>
+  </si>
+  <si>
+    <t>"ราคาทอง"</t>
+  </si>
+  <si>
+    <t>แม่ ทอง สุก</t>
+  </si>
+  <si>
+    <t>"ร้านทอง ฟิวเจอร์"</t>
+  </si>
+  <si>
+    <t>"ทองแท่ง เยาวราช กรุงเทพ"</t>
+  </si>
+  <si>
+    <t>"ร้านทอง ซีคอน"</t>
+  </si>
+  <si>
+    <t>paused; low quality; campaign paused</t>
+  </si>
+  <si>
+    <t>[ห้างทองฮั่วเซ่งเฮง]</t>
+  </si>
+  <si>
+    <t>"ราคาทองวันนี้"</t>
+  </si>
+  <si>
+    <t>"ทองวันนี้"</t>
+  </si>
+  <si>
     <t>[ทองคำราคา]</t>
   </si>
   <si>
-    <t>Exact match</t>
-  </si>
-  <si>
-    <t>4040 | ONN | Search Brand Traffic | Always On</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Eligible</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>THB</t>
+    <t>"ซื้อทองออนไลน์"</t>
+  </si>
+  <si>
+    <t>[Hua Seng Heng]</t>
+  </si>
+  <si>
+    <t>"ร้านทอง โลตัส"</t>
+  </si>
+  <si>
+    <t>"ห้างทองเยาวราช ราคา"</t>
+  </si>
+  <si>
+    <t>"ราคาทองห้างเยาวราช"</t>
+  </si>
+  <si>
+    <t>"ราคา ห้างทองเยาวราช"</t>
+  </si>
+  <si>
+    <t>"ราคาทอง ร้านทองเยาวราช กรุงเทพ"</t>
+  </si>
+  <si>
+    <t>[Gold now]</t>
+  </si>
+  <si>
+    <t>[ห้างทองเยาวราช]</t>
+  </si>
+  <si>
+    <t>[ฮั่วเซ่งเฮง]</t>
+  </si>
+  <si>
+    <t>"ร้านทอง เซ็นทรัล"</t>
+  </si>
+  <si>
+    <t>"ร้านทอง บิ๊กซี"</t>
   </si>
   <si>
     <t>"ออโรร่า ใกล้ฉัน"</t>
   </si>
   <si>
-    <t>Phrase match</t>
-  </si>
-  <si>
-    <t>"ราคา ห้างทองเยาวราช"</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
     <t>[แม่ทองใบ]</t>
   </si>
   <si>
+    <t>"ร้านขายทอง"</t>
+  </si>
+  <si>
+    <t>[ห้างทองแม่ทองสุก]</t>
+  </si>
+  <si>
+    <t>"ร้านทองเยาวราช"</t>
+  </si>
+  <si>
+    <t>"ราคาทอง ร้านทองเยาวราช"</t>
+  </si>
+  <si>
+    <t>[aurora]</t>
+  </si>
+  <si>
     <t>[ห้าง ทอง เยาวราช กรุงเทพ ใกล้ ฉัน]</t>
   </si>
   <si>
+    <t>"ร้านห้างทองเยาวราช"</t>
+  </si>
+  <si>
+    <t>"ทองสมาคม"</t>
+  </si>
+  <si>
+    <t>"www hua seng heng com"</t>
+  </si>
+  <si>
+    <t>"กรอบพระ ร้านทอง"</t>
+  </si>
+  <si>
+    <t>ร้าน ทอง ใกล้ ฉัน</t>
+  </si>
+  <si>
+    <t>"แอปทอง ออนไลน์"</t>
+  </si>
+  <si>
+    <t>"เลี่ยมพระ ร้านทอง"</t>
+  </si>
+  <si>
+    <t>"ห้าง ทอง ทอง เยาวราช"</t>
+  </si>
+  <si>
+    <t>"ร้านทอง เปิดวันอาทิตย์"</t>
+  </si>
+  <si>
+    <t>"สมาคมทองคำ"</t>
+  </si>
+  <si>
     <t>"ร้านทองแท้"</t>
   </si>
   <si>
-    <t>"ร้านทองกรุงเทพเยาวราช"</t>
-  </si>
-  <si>
-    <t>[ห้างทองฮั่วเซ่งเฮง]</t>
-  </si>
-  <si>
-    <t>Paused</t>
-  </si>
-  <si>
-    <t>"ร้านทอ"</t>
-  </si>
-  <si>
-    <t>paused</t>
-  </si>
-  <si>
-    <t>[Hua Seng Heng]</t>
-  </si>
-  <si>
-    <t>"ราคาทองวันนี้"</t>
-  </si>
-  <si>
-    <t>"ร้านทองใกล้ฉัน"</t>
-  </si>
-  <si>
-    <t>"ราคาทองห้างเยาวราช"</t>
-  </si>
-  <si>
-    <t>ร้าน ทอง ใกล้ ฉัน</t>
-  </si>
-  <si>
-    <t>Broad match</t>
-  </si>
-  <si>
-    <t>"ทองสมาคม"</t>
-  </si>
-  <si>
-    <t>"ห้าง ทอง ทอง เยาวราช"</t>
-  </si>
-  <si>
-    <t>"ห้างทองเยาวราช ราคา"</t>
-  </si>
-  <si>
-    <t>"ร้านทอง บิ๊กซี"</t>
-  </si>
-  <si>
-    <t>"ทองกรุงเทพเยาวราช"</t>
-  </si>
-  <si>
-    <t>"ร้านทอง ฟิวเจอร์"</t>
-  </si>
-  <si>
-    <t>[ห้าง ทอง ออ โร ร่า ใกล้ ฉัน]</t>
-  </si>
-  <si>
-    <t>"ร้านทอง เปิดวันอาทิตย์"</t>
-  </si>
-  <si>
-    <t>"กรอบพระ ร้านทอง"</t>
-  </si>
-  <si>
-    <t>[ฮั่วเซ่งเฮง]</t>
-  </si>
-  <si>
-    <t>"ราคาทอง ร้านทองเยาวราช กรุงเทพ"</t>
-  </si>
-  <si>
-    <t>"ร้านทองออนไลน์"</t>
-  </si>
-  <si>
-    <t>"ร้านเพชรทองออโรร่า"</t>
-  </si>
-  <si>
-    <t>ห้างทองใกล้ฉัน</t>
-  </si>
-  <si>
-    <t>"www hua seng heng com"</t>
-  </si>
-  <si>
-    <t>"ราคาทอง ร้านทองเยาวราช"</t>
-  </si>
-  <si>
-    <t>[Bangkok Golds]</t>
-  </si>
-  <si>
-    <t>"ร้านทอง ซีคอน"</t>
-  </si>
-  <si>
-    <t>Limited</t>
-  </si>
-  <si>
-    <t>low quality</t>
-  </si>
-  <si>
-    <t>[ห้างทองแม่ทองสุก]</t>
-  </si>
-  <si>
-    <t>"ทองแท่ง เยาวราช กรุงเทพ"</t>
-  </si>
-  <si>
-    <t>"ทองวันนี้"</t>
-  </si>
-  <si>
-    <t>"ราคาทอง"</t>
-  </si>
-  <si>
-    <t>"เลี่ยมพระ ร้านทอง"</t>
-  </si>
-  <si>
-    <t>"ร้านทอง โรบินสัน"</t>
-  </si>
-  <si>
-    <t>แม่ ทอง สุก</t>
-  </si>
-  <si>
-    <t>"ซื้อทองออนไลน์"</t>
-  </si>
-  <si>
-    <t>"ร้านทอง โลตัส"</t>
-  </si>
-  <si>
-    <t>"ร้านทองเยาวราช"</t>
-  </si>
-  <si>
-    <t>"ร้านทอง เซ็นทรัล"</t>
-  </si>
-  <si>
-    <t>[Gold now]</t>
-  </si>
-  <si>
-    <t>"แอปทอง ออนไลน์"</t>
-  </si>
-  <si>
-    <t>[aurora]</t>
-  </si>
-  <si>
-    <t>"สมาคมทองคำ"</t>
-  </si>
-  <si>
-    <t>[ห้าง ทอง เยาวราช กรุงเทพ]</t>
-  </si>
-  <si>
     <t>"ห้างทองเยาวราช ราคาทอง"</t>
   </si>
   <si>
-    <t>[ห้างทองเยาวราช]</t>
-  </si>
-  <si>
-    <t>"ร้านขายทอง"</t>
-  </si>
-  <si>
-    <t>"ร้านห้างทองเยาวราช"</t>
+    <t>"สร้อยทอง 2 สลึง"</t>
+  </si>
+  <si>
+    <t>Generic</t>
+  </si>
+  <si>
+    <t>"สร้อย สามกษัตริย์ ออ โร ร่า"</t>
+  </si>
+  <si>
+    <t>"aurora ทอง สาขา"</t>
+  </si>
+  <si>
+    <t>"ของขวัญ วัน เกิด ทอง"</t>
+  </si>
+  <si>
+    <t>"ทอง แท่ง 5 บาท ออ โร ร่า"</t>
+  </si>
+  <si>
+    <t>"กุหลาบ ทอง ออ โร ร่า"</t>
+  </si>
+  <si>
+    <t>"ซื้อขาย ทอง ออนไลน์ ออ โร ร่า"</t>
+  </si>
+  <si>
+    <t>"พระ เลี่ยม ทอง ออ โร ร่า"</t>
   </si>
   <si>
     <t>"ราคา ทอง 1 สลึง วัน นี้ aurora"</t>
   </si>
   <si>
-    <t>Generic</t>
-  </si>
-  <si>
-    <t>"ทอง แท่ง 5 บาท ออ โร ร่า"</t>
+    <t>"แหวน ทอง 1 กรัม aurora"</t>
+  </si>
+  <si>
+    <t>"aurora gold สาขา"</t>
   </si>
   <si>
     <t>"โปร aurora"</t>
   </si>
   <si>
-    <t>"กุหลาบ ทอง ออ โร ร่า"</t>
-  </si>
-  <si>
-    <t>"สร้อย สามกษัตริย์ ออ โร ร่า"</t>
-  </si>
-  <si>
-    <t>"ของขวัญ วัน เกิด ทอง"</t>
-  </si>
-  <si>
-    <t>"ซื้อขาย ทอง ออนไลน์ ออ โร ร่า"</t>
-  </si>
-  <si>
     <t>"ทอง 99.99 ออ โร ร่า"</t>
   </si>
   <si>
-    <t>"สร้อยทอง 2 สลึง"</t>
-  </si>
-  <si>
     <t>"แบรนด์ aurora"</t>
-  </si>
-  <si>
-    <t>"แหวน ทอง 1 กรัม aurora"</t>
-  </si>
-  <si>
-    <t>"aurora ทอง สาขา"</t>
-  </si>
-  <si>
-    <t>"พระ เลี่ยม ทอง ออ โร ร่า"</t>
-  </si>
-  <si>
-    <t>"aurora gold สาขา"</t>
   </si>
 </sst>
 </file>
@@ -663,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -746,22 +743,22 @@
         <v>23</v>
       </c>
       <c r="I4">
-        <v>10.92</v>
+        <v>0.33</v>
       </c>
       <c r="J4">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="K4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0.68</v>
+        <v>0.33</v>
       </c>
       <c r="M4" s="1">
-        <v>0.1111</v>
+        <v>3.1300000000000001E-2</v>
       </c>
       <c r="N4" s="1">
-        <v>0.43569999999999998</v>
+        <v>0.88239999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -790,22 +787,22 @@
         <v>23</v>
       </c>
       <c r="I5">
-        <v>14.02</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="J5">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>4.67</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="M5" s="1">
-        <v>5.0799999999999998E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="N5" s="1">
-        <v>0.56669999999999998</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -834,33 +831,33 @@
         <v>23</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>20.49</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" t="s">
-        <v>27</v>
+        <v>1.86</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.28210000000000002</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0.625</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -869,10 +866,10 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H7" t="s">
         <v>23</v>
@@ -881,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -889,11 +886,11 @@
       <c r="L7">
         <v>0</v>
       </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
+      <c r="M7" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -901,7 +898,7 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -922,22 +919,22 @@
         <v>23</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>27</v>
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.69230000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -945,7 +942,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -966,22 +963,22 @@
         <v>23</v>
       </c>
       <c r="I9">
-        <v>26.43</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="J9">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="K9">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="M9" s="1">
-        <v>9.9400000000000002E-2</v>
+        <v>0.26669999999999999</v>
       </c>
       <c r="N9" s="1">
-        <v>0.68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -989,7 +986,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
@@ -1010,19 +1007,19 @@
         <v>23</v>
       </c>
       <c r="I10">
-        <v>0.88</v>
+        <v>1.44</v>
       </c>
       <c r="J10">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="M10" s="1">
-        <v>4.4400000000000002E-2</v>
+        <v>5.45E-2</v>
       </c>
       <c r="N10" s="1">
         <v>0</v>
@@ -1033,10 +1030,10 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
@@ -1054,30 +1051,30 @@
         <v>23</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>144.97</v>
       </c>
       <c r="J11">
-        <v>58</v>
+        <v>1443</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
+        <v>5.96E-2</v>
       </c>
       <c r="N11" s="1">
-        <v>0.5</v>
+        <v>0.6492</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
         <v>25</v>
@@ -1089,31 +1086,31 @@
         <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s">
         <v>23</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>45.55</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" t="s">
-        <v>27</v>
+        <v>1.82</v>
+      </c>
+      <c r="M12" s="1">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0.59799999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1121,7 +1118,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -1142,22 +1139,22 @@
         <v>23</v>
       </c>
       <c r="I13">
-        <v>12.24</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1">
-        <v>7.8399999999999997E-2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="1">
-        <v>0.47620000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1165,7 +1162,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
         <v>25</v>
@@ -1186,22 +1183,22 @@
         <v>23</v>
       </c>
       <c r="I14">
-        <v>154.11000000000001</v>
+        <v>7.55</v>
       </c>
       <c r="J14">
-        <v>1027</v>
+        <v>47</v>
       </c>
       <c r="K14">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="L14">
-        <v>1.1200000000000001</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M14" s="1">
-        <v>0.13339999999999999</v>
+        <v>0.27660000000000001</v>
       </c>
       <c r="N14" s="1">
-        <v>0.38300000000000001</v>
+        <v>0.90239999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1209,7 +1206,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
@@ -1230,22 +1227,22 @@
         <v>23</v>
       </c>
       <c r="I15">
-        <v>43.95</v>
+        <v>240.02</v>
       </c>
       <c r="J15">
-        <v>355</v>
+        <v>1813</v>
       </c>
       <c r="K15">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="L15">
-        <v>1.91</v>
+        <v>0.68</v>
       </c>
       <c r="M15" s="1">
-        <v>6.4799999999999996E-2</v>
+        <v>0.1953</v>
       </c>
       <c r="N15" s="1">
-        <v>0.55810000000000004</v>
+        <v>0.51239999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1253,10 +1250,10 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
@@ -1274,22 +1271,22 @@
         <v>23</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>194.94</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>721</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16" t="s">
-        <v>27</v>
-      </c>
-      <c r="N16" t="s">
-        <v>27</v>
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1297,10 +1294,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
@@ -1318,22 +1315,22 @@
         <v>23</v>
       </c>
       <c r="I17">
-        <v>262.35000000000002</v>
+        <v>6.74</v>
       </c>
       <c r="J17">
-        <v>2126</v>
+        <v>74</v>
       </c>
       <c r="K17">
-        <v>296</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>0.89</v>
+        <v>1.69</v>
       </c>
       <c r="M17" s="1">
-        <v>0.13919999999999999</v>
+        <v>5.4100000000000002E-2</v>
       </c>
       <c r="N17" s="1">
-        <v>0.62329999999999997</v>
+        <v>0.52170000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1374,15 +1371,15 @@
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
         <v>43</v>
@@ -1397,31 +1394,31 @@
         <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s">
         <v>23</v>
       </c>
       <c r="I19">
-        <v>1.1100000000000001</v>
+        <v>6.01</v>
       </c>
       <c r="J19">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0.55000000000000004</v>
+        <v>6.01</v>
       </c>
       <c r="M19" s="1">
-        <v>3.4500000000000003E-2</v>
+        <v>0.1111</v>
       </c>
       <c r="N19" s="1">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1429,10 +1426,10 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
@@ -1453,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1465,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1473,7 +1470,7 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
@@ -1494,22 +1491,22 @@
         <v>23</v>
       </c>
       <c r="I21">
-        <v>71.59</v>
+        <v>158.15</v>
       </c>
       <c r="J21">
-        <v>114</v>
+        <v>1161</v>
       </c>
       <c r="K21">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="L21">
-        <v>3.58</v>
+        <v>1.01</v>
       </c>
       <c r="M21" s="1">
-        <v>0.1754</v>
+        <v>0.13519999999999999</v>
       </c>
       <c r="N21" s="1">
-        <v>0.63790000000000002</v>
+        <v>0.38940000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1517,7 +1514,7 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
@@ -1538,22 +1535,22 @@
         <v>23</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="J22">
-        <v>27</v>
+        <v>170</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
+        <v>0.15290000000000001</v>
       </c>
       <c r="N22" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1561,10 +1558,10 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
         <v>19</v>
@@ -1582,22 +1579,22 @@
         <v>23</v>
       </c>
       <c r="I23">
-        <v>6.74</v>
+        <v>12.29</v>
       </c>
       <c r="J23">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="L23">
-        <v>1.69</v>
+        <v>0.53</v>
       </c>
       <c r="M23" s="1">
-        <v>7.5499999999999998E-2</v>
+        <v>0.1278</v>
       </c>
       <c r="N23" s="1">
-        <v>0.52939999999999998</v>
+        <v>0.42609999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1605,10 +1602,10 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
         <v>19</v>
@@ -1626,22 +1623,22 @@
         <v>23</v>
       </c>
       <c r="I24">
-        <v>6.43</v>
+        <v>23.02</v>
       </c>
       <c r="J24">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="K24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>1.29</v>
+        <v>2.88</v>
       </c>
       <c r="M24" s="1">
-        <v>0.25</v>
+        <v>0.13789999999999999</v>
       </c>
       <c r="N24" s="1">
-        <v>0.9</v>
+        <v>0.80700000000000005</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1649,10 +1646,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
         <v>19</v>
@@ -1670,22 +1667,22 @@
         <v>23</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>12.24</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="s">
-        <v>27</v>
-      </c>
-      <c r="N25" t="s">
-        <v>27</v>
+        <v>1.53</v>
+      </c>
+      <c r="M25" s="1">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0.43480000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -1693,7 +1690,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
@@ -1714,22 +1711,22 @@
         <v>23</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>64.25</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>27</v>
+        <v>0.1862</v>
+      </c>
+      <c r="N26" s="1">
+        <v>0.55710000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -1737,10 +1734,10 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
         <v>19</v>
@@ -1758,22 +1755,22 @@
         <v>23</v>
       </c>
       <c r="I27">
-        <v>9.89</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>1.24E-2</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1">
-        <v>0.33750000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -1781,7 +1778,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
         <v>25</v>
@@ -1814,10 +1811,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N28" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -1825,7 +1822,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
         <v>25</v>
@@ -1846,22 +1843,22 @@
         <v>23</v>
       </c>
       <c r="I29">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>0.47</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0.2727</v>
-      </c>
-      <c r="N29" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M29" t="s">
+        <v>30</v>
+      </c>
+      <c r="N29" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -1869,7 +1866,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
         <v>25</v>
@@ -1890,22 +1887,22 @@
         <v>23</v>
       </c>
       <c r="I30">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0.1389</v>
-      </c>
-      <c r="N30" s="1">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>30</v>
+      </c>
+      <c r="N30" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -1913,10 +1910,10 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
         <v>19</v>
@@ -1934,22 +1931,22 @@
         <v>23</v>
       </c>
       <c r="I31">
-        <v>117.88</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>1176</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>1.73</v>
-      </c>
-      <c r="M31" s="1">
-        <v>5.7799999999999997E-2</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0.6512</v>
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>30</v>
+      </c>
+      <c r="N31" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1957,10 +1954,10 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
         <v>19</v>
@@ -1978,22 +1975,22 @@
         <v>23</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32" t="s">
-        <v>27</v>
-      </c>
-      <c r="N32" t="s">
-        <v>27</v>
+        <v>0.86</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="N32" s="1">
+        <v>0.73329999999999995</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2001,10 +1998,10 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D33" t="s">
         <v>19</v>
@@ -2022,22 +2019,22 @@
         <v>23</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>17.03</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33" t="s">
-        <v>27</v>
-      </c>
-      <c r="N33" t="s">
-        <v>27</v>
+        <v>5.68</v>
+      </c>
+      <c r="M33" s="1">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0.35630000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2045,10 +2042,10 @@
         <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -2066,22 +2063,22 @@
         <v>23</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>59.73</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>292</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M34" s="1">
-        <v>0</v>
+        <v>0.1507</v>
       </c>
       <c r="N34" s="1">
-        <v>0</v>
+        <v>0.4032</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2089,7 +2086,7 @@
         <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
         <v>25</v>
@@ -2101,31 +2098,31 @@
         <v>20</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H35" t="s">
         <v>23</v>
       </c>
       <c r="I35">
-        <v>6.01</v>
+        <v>72.91</v>
       </c>
       <c r="J35">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L35">
-        <v>6.01</v>
+        <v>3.31</v>
       </c>
       <c r="M35" s="1">
-        <v>0.125</v>
+        <v>0.16919999999999999</v>
       </c>
       <c r="N35" s="1">
-        <v>0.4</v>
+        <v>0.62319999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2133,10 +2130,10 @@
         <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
         <v>19</v>
@@ -2154,22 +2151,22 @@
         <v>23</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="J36">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="M36" s="1">
-        <v>0</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="N36" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.56520000000000004</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -2177,10 +2174,10 @@
         <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
         <v>19</v>
@@ -2201,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -2209,11 +2206,11 @@
       <c r="L37">
         <v>0</v>
       </c>
-      <c r="M37" t="s">
-        <v>27</v>
-      </c>
-      <c r="N37" t="s">
-        <v>27</v>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2221,7 +2218,7 @@
         <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
         <v>25</v>
@@ -2242,22 +2239,22 @@
         <v>23</v>
       </c>
       <c r="I38">
-        <v>68.16</v>
+        <v>15.56</v>
       </c>
       <c r="J38">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="K38">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="M38" s="1">
-        <v>0.16539999999999999</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="N38" s="1">
-        <v>0.50390000000000001</v>
+        <v>0.65080000000000005</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2265,10 +2262,10 @@
         <v>16</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
         <v>19</v>
@@ -2286,22 +2283,22 @@
         <v>23</v>
       </c>
       <c r="I39">
-        <v>212.67</v>
+        <v>3.38</v>
       </c>
       <c r="J39">
-        <v>1371</v>
+        <v>20</v>
       </c>
       <c r="K39">
-        <v>274</v>
+        <v>1</v>
       </c>
       <c r="L39">
-        <v>0.78</v>
+        <v>3.38</v>
       </c>
       <c r="M39" s="1">
-        <v>0.19989999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="N39" s="1">
-        <v>0.53200000000000003</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2309,7 +2306,7 @@
         <v>16</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
         <v>25</v>
@@ -2330,22 +2327,22 @@
         <v>23</v>
       </c>
       <c r="I40">
-        <v>1.1100000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="J40">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="K40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L40">
-        <v>1.1100000000000001</v>
+        <v>2.61</v>
       </c>
       <c r="M40" s="1">
-        <v>7.6899999999999996E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="N40" s="1">
-        <v>1</v>
+        <v>0.54549999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2353,7 +2350,7 @@
         <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C41" t="s">
         <v>25</v>
@@ -2374,22 +2371,22 @@
         <v>23</v>
       </c>
       <c r="I41">
-        <v>19.39</v>
+        <v>0</v>
       </c>
       <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
         <v>30</v>
       </c>
-      <c r="K41">
-        <v>9</v>
-      </c>
-      <c r="L41">
-        <v>2.15</v>
-      </c>
-      <c r="M41" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="N41" s="1">
-        <v>0.66669999999999996</v>
+      <c r="N41" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -2397,10 +2394,10 @@
         <v>16</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
         <v>19</v>
@@ -2418,22 +2415,22 @@
         <v>23</v>
       </c>
       <c r="I42">
-        <v>129.91</v>
+        <v>183.76</v>
       </c>
       <c r="J42">
-        <v>607</v>
+        <v>901</v>
       </c>
       <c r="K42">
-        <v>19</v>
+        <v>554</v>
       </c>
       <c r="L42">
-        <v>6.84</v>
+        <v>0.33</v>
       </c>
       <c r="M42" s="1">
-        <v>3.1300000000000001E-2</v>
+        <v>0.6149</v>
       </c>
       <c r="N42" s="1">
-        <v>0.62729999999999997</v>
+        <v>0.96799999999999997</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2441,10 +2438,10 @@
         <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
         <v>19</v>
@@ -2462,22 +2459,22 @@
         <v>23</v>
       </c>
       <c r="I43">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="K43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M43" s="1">
-        <v>0.129</v>
-      </c>
-      <c r="N43" s="1">
-        <v>0.86670000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -2485,7 +2482,7 @@
         <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" t="s">
         <v>25</v>
@@ -2506,22 +2503,22 @@
         <v>23</v>
       </c>
       <c r="I44">
-        <v>27.27</v>
+        <v>1.01</v>
       </c>
       <c r="J44">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="K44">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L44">
-        <v>1.0900000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="M44" s="1">
-        <v>0.1953</v>
-      </c>
-      <c r="N44" s="1">
-        <v>0.52</v>
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="N44" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -2529,7 +2526,7 @@
         <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C45" t="s">
         <v>25</v>
@@ -2550,22 +2547,22 @@
         <v>23</v>
       </c>
       <c r="I45">
-        <v>7.67</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>3.84</v>
-      </c>
-      <c r="M45" s="1">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="N45" s="1">
-        <v>0.58819999999999995</v>
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>30</v>
+      </c>
+      <c r="N45" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -2573,7 +2570,7 @@
         <v>16</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C46" t="s">
         <v>25</v>
@@ -2594,22 +2591,22 @@
         <v>23</v>
       </c>
       <c r="I46">
-        <v>48.46</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>1.56</v>
-      </c>
-      <c r="M46" s="1">
-        <v>0.1409</v>
-      </c>
-      <c r="N46" s="1">
-        <v>0.40450000000000003</v>
+        <v>0</v>
+      </c>
+      <c r="M46" t="s">
+        <v>30</v>
+      </c>
+      <c r="N46" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -2617,10 +2614,10 @@
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C47" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D47" t="s">
         <v>19</v>
@@ -2641,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -2649,11 +2646,11 @@
       <c r="L47">
         <v>0</v>
       </c>
-      <c r="M47" t="s">
-        <v>27</v>
+      <c r="M47" s="1">
+        <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -2661,10 +2658,10 @@
         <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D48" t="s">
         <v>19</v>
@@ -2682,22 +2679,22 @@
         <v>23</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>337.06</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>2684</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="s">
-        <v>27</v>
-      </c>
-      <c r="N48" t="s">
-        <v>27</v>
+        <v>0.8</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0.1565</v>
+      </c>
+      <c r="N48" s="1">
+        <v>0.64319999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -2705,10 +2702,10 @@
         <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
         <v>19</v>
@@ -2726,22 +2723,22 @@
         <v>23</v>
       </c>
       <c r="I49">
-        <v>135.41999999999999</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>659</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>0.34</v>
-      </c>
-      <c r="M49" s="1">
-        <v>0.60240000000000005</v>
-      </c>
-      <c r="N49" s="1">
-        <v>0.96679999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="M49" t="s">
+        <v>30</v>
+      </c>
+      <c r="N49" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -2749,7 +2746,7 @@
         <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C50" t="s">
         <v>25</v>
@@ -2770,22 +2767,22 @@
         <v>23</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="s">
-        <v>27</v>
-      </c>
-      <c r="N50" t="s">
-        <v>27</v>
+        <v>0.83</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0.1176</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -2793,10 +2790,10 @@
         <v>16</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
@@ -2814,22 +2811,22 @@
         <v>23</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="J51">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M51" s="1">
-        <v>0</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="N51" s="1">
-        <v>0.90910000000000002</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -2837,7 +2834,7 @@
         <v>16</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
         <v>25</v>
@@ -2870,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="M52" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -2881,10 +2878,10 @@
         <v>16</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
         <v>19</v>
@@ -2902,22 +2899,22 @@
         <v>23</v>
       </c>
       <c r="I53">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>0.86</v>
-      </c>
-      <c r="M53" s="1">
-        <v>6.25E-2</v>
-      </c>
-      <c r="N53" s="1">
-        <v>0.83330000000000004</v>
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
+        <v>30</v>
+      </c>
+      <c r="N53" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -2925,7 +2922,7 @@
         <v>16</v>
       </c>
       <c r="B54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C54" t="s">
         <v>25</v>
@@ -2946,22 +2943,22 @@
         <v>23</v>
       </c>
       <c r="I54">
-        <v>13.51</v>
+        <v>31.62</v>
       </c>
       <c r="J54">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="K54">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="L54">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="M54" s="1">
-        <v>4.8399999999999999E-2</v>
+        <v>0.10050000000000001</v>
       </c>
       <c r="N54" s="1">
-        <v>0.625</v>
+        <v>0.68420000000000003</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -2969,7 +2966,7 @@
         <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C55" t="s">
         <v>25</v>
@@ -2990,22 +2987,22 @@
         <v>23</v>
       </c>
       <c r="I55">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="J55">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55">
-        <v>0.51</v>
-      </c>
-      <c r="M55" s="1">
-        <v>2.4400000000000002E-2</v>
+        <v>0</v>
+      </c>
+      <c r="M55" t="s">
+        <v>30</v>
       </c>
       <c r="N55" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -3013,17 +3010,17 @@
         <v>16</v>
       </c>
       <c r="B56" t="s">
+        <v>81</v>
+      </c>
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" t="s">
         <v>82</v>
       </c>
-      <c r="C56" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" t="s">
-        <v>83</v>
-      </c>
       <c r="F56" t="s">
         <v>21</v>
       </c>
@@ -3034,22 +3031,22 @@
         <v>23</v>
       </c>
       <c r="I56">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="M56" s="1">
-        <v>0.18179999999999999</v>
+        <v>0</v>
       </c>
       <c r="N56" s="1">
-        <v>0.7</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -3057,7 +3054,7 @@
         <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C57" t="s">
         <v>25</v>
@@ -3066,7 +3063,7 @@
         <v>19</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F57" t="s">
         <v>21</v>
@@ -3078,22 +3075,22 @@
         <v>23</v>
       </c>
       <c r="I57">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>0.17</v>
-      </c>
-      <c r="M57" s="1">
-        <v>1</v>
-      </c>
-      <c r="N57" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M57" t="s">
+        <v>30</v>
+      </c>
+      <c r="N57" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -3101,7 +3098,7 @@
         <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
         <v>25</v>
@@ -3110,7 +3107,7 @@
         <v>19</v>
       </c>
       <c r="E58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F58" t="s">
         <v>21</v>
@@ -3122,22 +3119,22 @@
         <v>23</v>
       </c>
       <c r="I58">
-        <v>1.65</v>
+        <v>62.77</v>
       </c>
       <c r="J58">
-        <v>22</v>
+        <v>167</v>
       </c>
       <c r="K58">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="L58">
-        <v>0.83</v>
+        <v>3.3</v>
       </c>
       <c r="M58" s="1">
-        <v>9.0899999999999995E-2</v>
+        <v>0.1138</v>
       </c>
       <c r="N58" s="1">
-        <v>0.77270000000000005</v>
+        <v>0.51019999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -3145,7 +3142,7 @@
         <v>16</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
         <v>25</v>
@@ -3154,7 +3151,7 @@
         <v>19</v>
       </c>
       <c r="E59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F59" t="s">
         <v>21</v>
@@ -3178,10 +3175,10 @@
         <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N59" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -3189,7 +3186,7 @@
         <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
         <v>25</v>
@@ -3198,7 +3195,7 @@
         <v>19</v>
       </c>
       <c r="E60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F60" t="s">
         <v>21</v>
@@ -3210,22 +3207,22 @@
         <v>23</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60" t="s">
-        <v>27</v>
-      </c>
-      <c r="N60" t="s">
-        <v>27</v>
+        <v>0.17</v>
+      </c>
+      <c r="M60" s="1">
+        <v>1</v>
+      </c>
+      <c r="N60" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
@@ -3233,7 +3230,7 @@
         <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C61" t="s">
         <v>25</v>
@@ -3242,7 +3239,7 @@
         <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F61" t="s">
         <v>21</v>
@@ -3266,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N61" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
@@ -3277,7 +3274,7 @@
         <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C62" t="s">
         <v>25</v>
@@ -3286,7 +3283,7 @@
         <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F62" t="s">
         <v>21</v>
@@ -3321,7 +3318,7 @@
         <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s">
         <v>25</v>
@@ -3330,7 +3327,7 @@
         <v>19</v>
       </c>
       <c r="E63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F63" t="s">
         <v>21</v>
@@ -3345,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -3353,11 +3350,11 @@
       <c r="L63">
         <v>0</v>
       </c>
-      <c r="M63" t="s">
-        <v>27</v>
-      </c>
-      <c r="N63" t="s">
-        <v>27</v>
+      <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
@@ -3365,7 +3362,7 @@
         <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s">
         <v>25</v>
@@ -3374,7 +3371,7 @@
         <v>19</v>
       </c>
       <c r="E64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F64" t="s">
         <v>21</v>
@@ -3386,22 +3383,22 @@
         <v>23</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J64">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="M64" s="1">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="N64" s="1">
-        <v>0.33329999999999999</v>
+        <v>0.69230000000000003</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
@@ -3409,7 +3406,7 @@
         <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C65" t="s">
         <v>25</v>
@@ -3418,7 +3415,7 @@
         <v>19</v>
       </c>
       <c r="E65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F65" t="s">
         <v>21</v>
@@ -3430,22 +3427,22 @@
         <v>23</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J65">
         <v>1</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
@@ -3453,7 +3450,7 @@
         <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C66" t="s">
         <v>25</v>
@@ -3462,7 +3459,7 @@
         <v>19</v>
       </c>
       <c r="E66" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F66" t="s">
         <v>21</v>
@@ -3474,22 +3471,22 @@
         <v>23</v>
       </c>
       <c r="I66">
-        <v>0.17</v>
+        <v>70.55</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="L66">
-        <v>0.17</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="M66" s="1">
-        <v>1</v>
+        <v>0.20480000000000001</v>
       </c>
       <c r="N66" s="1">
-        <v>1</v>
+        <v>0.6421</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
@@ -3497,7 +3494,7 @@
         <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C67" t="s">
         <v>25</v>
@@ -3506,7 +3503,7 @@
         <v>19</v>
       </c>
       <c r="E67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F67" t="s">
         <v>21</v>
@@ -3518,22 +3515,22 @@
         <v>23</v>
       </c>
       <c r="I67">
-        <v>57.08</v>
+        <v>3.48</v>
       </c>
       <c r="J67">
-        <v>130</v>
+        <v>31</v>
       </c>
       <c r="K67">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L67">
-        <v>4.08</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="M67" s="1">
-        <v>0.1077</v>
+        <v>9.6799999999999997E-2</v>
       </c>
       <c r="N67" s="1">
-        <v>0.53849999999999998</v>
+        <v>0.7097</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
@@ -3541,7 +3538,7 @@
         <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C68" t="s">
         <v>25</v>
@@ -3550,7 +3547,7 @@
         <v>19</v>
       </c>
       <c r="E68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F68" t="s">
         <v>21</v>
@@ -3565,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -3573,11 +3570,11 @@
       <c r="L68">
         <v>0</v>
       </c>
-      <c r="M68" s="1">
-        <v>0</v>
-      </c>
-      <c r="N68" s="1">
-        <v>1</v>
+      <c r="M68" t="s">
+        <v>30</v>
+      </c>
+      <c r="N68" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
@@ -3585,7 +3582,7 @@
         <v>16</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C69" t="s">
         <v>25</v>
@@ -3594,7 +3591,7 @@
         <v>19</v>
       </c>
       <c r="E69" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F69" t="s">
         <v>21</v>
@@ -3606,23 +3603,45 @@
         <v>23</v>
       </c>
       <c r="I69">
-        <v>58.45</v>
+        <v>0</v>
       </c>
       <c r="J69">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="K69">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L69">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M69" s="1">
-        <v>0.16669999999999999</v>
+        <v>0</v>
       </c>
       <c r="N69" s="1">
-        <v>0.60319999999999996</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M72" s="1"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M77" s="1"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
